--- a/Sentences/report.xlsx
+++ b/Sentences/report.xlsx
@@ -413,28 +413,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Słowo (Lema)</t>
+          <t>Word (Lemma)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Ilość wystąpień ogółem</t>
+          <t>Total Occurrences</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Liczba unikalnych poprzedników</t>
+          <t>Unique Predecessors</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Dokładny kontekst (słowo i ilość)</t>
+          <t>Detailed Context (word and frequency)</t>
         </is>
       </c>
     </row>
@@ -445,14 +445,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C2" t="n">
         <v>40</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gdzie (8), rano (5), widzieć (3), migać (3), czekać (3), samochód (3), kochać (3), myśleć (3), szkoła (3), mieć (2), dzień (2), telefon (2), kot (2), noc (2), spać (1), pomysł (1), wczoraj (1), kiedy (1), tata (1), klucz (1), mówić (1), ja (1), lubić (1), dzisiaj (1), pomóc (1), zimny (1), mama (1), pies (1), brat (1), czas (1), pamiętać (1), woda (1), słyszeć (1), pić (1), kawa (1), iść (1), pracować (1), książka (1), ty (1), co (1)</t>
+          <t>gdzie (8), rano (5), widzieć (3), migać (3), czekać (3), samochód (3), kochać (3), dzień (2), telefon (2), myśleć (2), kot (2), szkoła (2), noc (2), spać (1), mieć (1), pomysł (1), wczoraj (1), kiedy (1), tata (1), klucz (1), mówić (1), ja (1), lubić (1), dzisiaj (1), pomóc (1), zimny (1), mama (1), pies (1), brat (1), czas (1), pamiętać (1), woda (1), słyszeć (1), pić (1), kawa (1), iść (1), pracować (1), książka (1), ty (1), co (1)</t>
         </is>
       </c>
     </row>
@@ -463,14 +463,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C3" t="n">
         <v>34</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>co (6), dlaczego (6), dziękować (4), kupić (4), czekać (4), ja (4), móc (3), kiedy (3), rano (2), iść (2), gdzie (2), książka (2), jak (1), wiedzieć (1), dzisiaj (1), mówić (1), smutny (1), myśleć (1), woda (1), dom (1), widzieć (1), kto (1), przepraszać (1), przyjaciel (1), jutro (1), wieczór (1), herbata (1), kawa (1), kobieta (1), pić (1), pies (1), wczoraj (1), chcieć (1), kot (1)</t>
+          <t>dlaczego (6), co (5), dziękować (4), kupić (4), czekać (4), ja (4), móc (3), kiedy (3), rano (2), iść (2), gdzie (2), książka (2), dzisiaj (1), jak (1), wiedzieć (1), mówić (1), smutny (1), myśleć (1), woda (1), dom (1), widzieć (1), kto (1), przepraszać (1), przyjaciel (1), jutro (1), wieczór (1), herbata (1), kawa (1), kobieta (1), pić (1), pies (1), wczoraj (1), chcieć (1), kot (1)</t>
         </is>
       </c>
     </row>
@@ -481,14 +481,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="n">
         <v>29</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>kupić (20), dlaczego (6), kochać (4), ty (4), chcieć (3), myśleć (3), mówić (2), mieć (2), słyszeć (2), jak (2), twój (1), stary (1), migać (1), dziękować (1), dzisiaj (1), pieniądz (1), tata (1), gdzie (1), zimny (1), klucz (1), spać (1), czekać (1), nie (1), robić (1), ja (1), widzieć (1), co (1), środa (1), lubić (1)</t>
+          <t>kupić (20), dlaczego (6), kochać (4), ty (4), chcieć (3), myśleć (3), mieć (3), mówić (2), słyszeć (2), jak (2), migać (1), twój (1), stary (1), dziękować (1), dzisiaj (1), pieniądz (1), tata (1), gdzie (1), zimny (1), klucz (1), spać (1), czekać (1), nie (1), robić (1), ja (1), widzieć (1), co (1), środa (1), lubić (1)</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" t="n">
         <v>34</v>
@@ -535,14 +535,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
         <v>30</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>pić (6), pomóc (4), ty (4), przepraszać (3), czekać (3), kupić (3), mieć (3), dom (3), chcieć (2), co (2), nie (2), dobry (2), iść (2), uczyć (2), spać (2), migać (1), myśleć (1), móc (1), kiedy (1), poniedziałek (1), robić (1), noc (1), czas (1), dlaczego (1), rozumieć (1), rok (1), ważny (1), wczoraj (1), rano (1), środa (1)</t>
+          <t>pić (6), pomóc (4), przepraszać (3), czekać (3), kupić (3), mieć (3), dom (3), ty (3), chcieć (2), co (2), nie (2), dobry (2), iść (2), uczyć (2), spać (2), migać (1), myśleć (1), móc (1), kiedy (1), poniedziałek (1), robić (1), noc (1), czas (1), dlaczego (1), rozumieć (1), rok (1), ważny (1), wczoraj (1), rano (1), środa (1)</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" t="n">
         <v>20</v>
@@ -646,11 +646,11 @@
         <v>59</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>nowy (12), stary (10), duży (4), czekać (4), rano (3), iść (2), mieć (2), klucz (2), pies (2), ja (2), mój (2), brat (2), my (1), nie (1), wieczór (1), dziadek (1), już (1), woda (1), pracować (1), wczoraj (1), praca (1), tata (1), uczyć (1), środa (1)</t>
+          <t>nowy (12), stary (10), duży (4), czekać (4), rano (3), iść (2), mieć (2), klucz (2), pies (2), ja (2), brat (2), my (1), nie (1), wieczór (1), dziadek (1), już (1), woda (1), pracować (1), wczoraj (1), praca (1), on (1), tata (1), uczyć (1), mój (1), środa (1)</t>
         </is>
       </c>
     </row>
@@ -697,14 +697,14 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>dlaczego (3), myśleć (3), gdzie (2), pamiętać (2), wczoraj (2), migać (2), pić (2), duży (1), ty (1), telefon (1), kobieta (1), mężczyzna (1), kiedy (1), mówić (1), dziękować (1), mały (1), czas (1), uczyć (1), dom (1), pracować (1), kawa (1), jak (1), rano (1), klucz (1), czwartek (1), wieczór (1)</t>
+          <t>dlaczego (3), myśleć (3), gdzie (2), pamiętać (2), wczoraj (2), migać (2), pić (2), duży (1), ty (1), telefon (1), kobieta (1), mężczyzna (1), kiedy (1), mówić (1), dziękować (1), mały (1), uczyć (1), dom (1), pracować (1), kawa (1), jak (1), rano (1), klucz (1), czwartek (1), wieczór (1)</t>
         </is>
       </c>
     </row>
@@ -769,14 +769,14 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" t="n">
         <v>25</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>dzisiaj (4), rano (4), ty (4), pies (3), poniedziałek (2), ja (2), musieć (2), teraz (2), chcieć (2), móc (2), kiedy (2), pomysł (2), już (1), kobieta (1), brat (1), my (1), zmęczony (1), jutro (1), wieczór (1), chory (1), samochód (1), on (1), zdrowy (1), mężczyzna (1), czwartek (1)</t>
+          <t>dzisiaj (4), rano (4), ty (4), pies (3), ja (2), musieć (2), teraz (2), chcieć (2), móc (2), kiedy (2), pomysł (2), już (1), kobieta (1), brat (1), poniedziałek (1), my (1), zmęczony (1), jutro (1), wieczór (1), chory (1), samochód (1), on (1), zdrowy (1), mężczyzna (1), czwartek (1)</t>
         </is>
       </c>
     </row>
@@ -837,54 +837,54 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SZKOŁA</t>
+          <t>BRAT</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>39</v>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>iść (7), nowy (5), ja (3), nie (2), migać (2), stary (2), wczoraj (1), dzisiaj (1), uczyć (1), klucz (1), zmęczony (1), ty (1), kobieta (1), kot (1), poniedziałek (1), pracować (1), rano (1), dzień (1), robić (1), kawa (1), woda (1), pies (1)</t>
+          <t>mój (15), chory (3), mały (3), twój (2), zmęczony (1), siostra (1), dom (1), nasz (1), gdzie (1), on (1), nowy (1), spać (1), ty (1), urodziny (1)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BRAT</t>
+          <t>PRACA</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>39</v>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>mój (17), chory (3), mały (3), twój (2), zmęczony (1), siostra (1), dom (1), gdzie (1), nowy (1), spać (1), ty (1), urodziny (1)</t>
+          <t>iść (9), mój (4), kolega (3), rano (3), ja (2), nowy (2), dobry (2), robić (1), telefon (1), dzień (1), smutny (1), czas (1), pomóc (1), pomysł (1), woda (1), zmęczony (1), kawa (1), stary (1), ty (1)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PRACA</t>
+          <t>SZKOŁA</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>iść (9), mój (4), kolega (3), rano (3), ja (2), nowy (2), dobry (2), robić (1), telefon (1), dzień (1), smutny (1), czas (1), pomóc (1), pomysł (1), woda (1), zmęczony (1), kawa (1), stary (1), ty (1)</t>
+          <t>iść (6), nowy (5), ja (3), nie (2), migać (2), stary (2), wczoraj (1), dzisiaj (1), uczyć (1), klucz (1), zmęczony (1), ty (1), kobieta (1), kot (1), poniedziałek (1), pracować (1), rano (1), dzień (1), robić (1), kawa (1), woda (1), pies (1)</t>
         </is>
       </c>
     </row>
@@ -902,187 +902,187 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>bardzo (15), jak (2), ty (2), dzień (1), mieć (1), wczoraj (1), myśleć (1), kupić (1), mój (1), zawsze (1), ten (1), chcieć (1), nie (1), dziękować (1), ważny (1), ja (1), taki (1), tata (1), pić (1)</t>
+          <t>bardzo (15), jak (2), ty (2), dzień (1), mieć (1), wczoraj (1), myśleć (1), kupić (1), mój (1), zawsze (1), ten (1), chcieć (1), nie (1), dziękować (1), ważny (1), my (1), taki (1), tata (1), pić (1)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DZIADEK</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>dom (6), babcia (5), mój (5), stary (1), wczoraj (1), kiedy (1), dlaczego (1), kawa (1), rano (1), wieczór (1)</t>
+          <t>kiedy (5), dlaczego (5), co (2), jak (2), myśleć (2), widzieć (1), nie (1), dziękować (1), czas (1), babcia (1), szkoła (1), dom (1)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SAMOCHÓD</t>
+          <t>DZIADEK</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>31</v>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>stary (13), nowy (4), mały (3), ten (3), twój (2), telefon (1), ja (1), tata (1), taki (1), mężczyzna (1), duży (1)</t>
+          <t>dom (6), babcia (5), mój (5), stary (1), wczoraj (1), kiedy (1), dlaczego (1), kawa (1), rano (1), wieczór (1)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>SAMOCHÓD</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>gdzie (3), co (2), dzień (2), kiedy (1), chcieć (1), ważny (1), dlaczego (1), iść (1), czas (1), rok (1), myśleć (1), wtorek (1)</t>
+          <t>stary (13), nowy (4), mały (3), ten (3), twój (2), telefon (1), ja (1), tata (1), taki (1), mężczyzna (1), duży (1)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KAWA</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>pić (7), gorący (7), ja (4), zimny (3), czas (3), iść (2), ile (2), herbata (1), duży (1)</t>
+          <t>gdzie (3), co (2), dzień (2), kiedy (1), chcieć (1), ważny (1), dlaczego (1), iść (1), czas (1), rok (1), myśleć (1), wtorek (1)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KIEDY</t>
+          <t>KAWA</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>30</v>
       </c>
       <c r="C32" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>lubić (4), czas (2), rano (2), kochać (1), pracować (1), migać (1), mama (1), rok (1), wiedzieć (1), pamiętać (1), słyszeć (1)</t>
+          <t>pić (7), gorący (7), ja (4), zimny (3), czas (3), iść (2), ile (2), herbata (1), duży (1)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MAŁY</t>
+          <t>KIEDY</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C33" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ten (8), mój (7), mieć (2), kupić (2), bardzo (1), ty (1), woda (1), telefon (1), twój (1), kobieta (1), wieczór (1), iść (1), mężczyzna (1)</t>
+          <t>lubić (4), czas (2), rano (2), kochać (1), pracować (1), migać (1), mama (1), rok (1), wiedzieć (1), pamiętać (1), słyszeć (1)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>MAŁY</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>wczoraj (7), kawa (2), pracować (2), praca (2), co (1), kolega (1), zimny (1), herbata (1), nie (1), woda (1), spać (1), dziadek (1), jutro (1), środa (1)</t>
+          <t>ten (8), mój (5), mieć (2), kupić (2), bardzo (1), ty (1), woda (1), telefon (1), twój (1), kobieta (1), wasz (1), on (1), wieczór (1), iść (1), mężczyzna (1)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GDZIE</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>wiedzieć (6), dzisiaj (1)</t>
+          <t>wczoraj (7), kawa (2), pracować (2), praca (2), co (1), kolega (1), zimny (1), herbata (1), nie (1), woda (1), spać (1), dziadek (1), jutro (1), środa (1)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LUBIĆ</t>
+          <t>GDZIE</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>27</v>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>bardzo (9), nie (4), brat (3), ty (2), my (2), on (1), ja (1), pies (1), rano (1), kobieta (1), babcia (1), kot (1)</t>
+          <t>wiedzieć (6), dzisiaj (1)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>LUBIĆ</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>27</v>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>kiedy (5), dlaczego (5), jak (2), co (2), widzieć (1), nie (1), myśleć (1), dziękować (1), babcia (1), dom (1)</t>
+          <t>bardzo (9), nie (4), brat (3), ty (2), my (2), on (1), ja (1), pies (1), rano (1), kobieta (1), babcia (1), kot (1)</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>mały (6), stary (3), pies (3), ten (2), duży (2), nowy (1), mieć (1), smutny (1), dom (1), noc (1), mój (1), lubić (1), mówić (1), kiedy (1)</t>
+          <t>mały (6), stary (3), pies (3), ten (2), duży (2), nowy (1), mieć (1), smutny (1), dom (1), noc (1), on (1), lubić (1), mówić (1), kiedy (1)</t>
         </is>
       </c>
     </row>
@@ -1143,54 +1143,54 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>WIEDZIEĆ</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>rozumieć (7), słyszeć (6), pamiętać (4), myśleć (3), wiedzieć (2)</t>
+          <t>ty (3), ja (3), chcieć (3), zawsze (2), dobry (2), wy (1), kto (1), nie (1), musieć (1), już (1)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>WIEDZIEĆ</t>
+          <t>UCZYĆ</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>25</v>
       </c>
       <c r="C42" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ty (3), ja (3), chcieć (3), zawsze (2), dobry (2), wy (1), kto (1), nie (1), musieć (1), już (1)</t>
+          <t>lubić (3), musieć (2), chcieć (2), siostra (1), szkoła (1), wy (1), dobry (1), praca (1), on (1), zawsze (1), rano (1), ty (1), pamiętać (1), wczoraj (1), jak (1), środa (1)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>UCZYĆ</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>25</v>
       </c>
       <c r="C43" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>lubić (3), musieć (2), chcieć (2), siostra (1), szkoła (1), dobry (1), praca (1), on (1), wy (1), zawsze (1), rano (1), ty (1), pamiętać (1), wczoraj (1), jak (1), środa (1)</t>
+          <t>rozumieć (6), słyszeć (6), pamiętać (4), myśleć (3), wiedzieć (2)</t>
         </is>
       </c>
     </row>
@@ -1215,79 +1215,79 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PONIEDZIAŁEK</t>
+          <t>PIENIĄDZ</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>25</v>
       </c>
       <c r="C45" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>dzisiaj (3), urodziny (3), zawsze (2), pieniądz (2), pracować (2), dlaczego (1), migać (1), samochód (1), dom (1), dziadek (1), jeść (1), brat (1), wczoraj (1)</t>
+          <t>duży (9), mieć (7), ile (4), mój (3), czas (1), samochód (1)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PIENIĄDZ</t>
+          <t>TELEFON</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>duży (9), mieć (7), ile (4), mój (3), czas (1), samochód (1)</t>
+          <t>nowy (9), stary (4), który (2), twój (2), mój (2), kupić (2), ważny (1), dzisiaj (1), mały (1)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TELEFON</t>
+          <t>MIGAĆ</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>24</v>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>nowy (9), stary (4), który (2), twój (2), mój (2), kupić (2), ważny (1), dzisiaj (1), mały (1)</t>
+          <t>uczyć (16), chcieć (2), myśleć (1), teraz (1), dobry (1), ja (1), on (1), mężczyzna (1)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MIGAĆ</t>
+          <t>WODA</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>24</v>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>uczyć (16), chcieć (2), myśleć (1), teraz (1), dobry (1), ja (1), on (1), mężczyzna (1)</t>
+          <t>gorący (5), pić (4), zimny (4), gdzie (2), dziękować (1), jeść (1), dlaczego (1), duży (1), ile (1), dziadek (1), ja (1), dobry (1)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MÓWIĆ</t>
+          <t>PONIEDZIAŁEK</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1298,79 +1298,79 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>co (5), ja (4), ty (3), tata (2), babcia (2), my (1), noc (1), duży (1), czas (1), wczoraj (1), on (1), rano (1), lubić (1)</t>
+          <t>urodziny (3), dzisiaj (2), zawsze (2), pieniądz (2), pracować (2), dlaczego (1), migać (1), samochód (1), dom (1), dziadek (1), jeść (1), brat (1), wczoraj (1)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WODA</t>
+          <t>MYŚLEĆ</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>24</v>
       </c>
       <c r="C50" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>gorący (5), pić (4), zimny (4), gdzie (2), dziękować (1), jeść (1), dlaczego (1), duży (1), ile (1), dziadek (1), ja (1), dobry (1)</t>
+          <t>zawsze (4), noc (4), ty (2), często (2), duży (2), słyszeć (1), mama (1), dzisiaj (1), dlaczego (1)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MYŚLEĆ</t>
+          <t>TATA</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C51" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>zawsze (4), noc (4), ty (2), często (2), duży (2), słyszeć (1), mama (1), dzisiaj (1), dlaczego (1)</t>
+          <t>mój (6), czekać (3), twój (2), samochód (2), ty (1), klucz (1), on (1), książka (1), dziękować (1), wesoły (1), stary (1)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TATA</t>
+          <t>PRZYJACIEL</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>23</v>
       </c>
       <c r="C52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>mój (7), czekać (3), twój (2), samochód (2), ty (1), klucz (1), książka (1), dziękować (1), wesoły (1), stary (1)</t>
+          <t>mój (10), twój (5), dobry (3), wesoły (1), stary (1), mały (1), nowy (1), książka (1)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PRZYJACIEL</t>
+          <t>MÓWIĆ</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>23</v>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>mój (10), twój (5), dobry (3), wesoły (1), stary (1), mały (1), nowy (1), książka (1)</t>
+          <t>co (5), ja (4), ty (2), tata (2), babcia (2), my (1), noc (1), duży (1), czas (1), wczoraj (1), on (1), rano (1), lubić (1)</t>
         </is>
       </c>
     </row>
@@ -1618,11 +1618,11 @@
         <v>17</v>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>twój (6), mój (5), mama (1), smutny (1), wesoły (1), czwartek (1)</t>
+          <t>mój (5), twój (5), mama (1), smutny (1), wesoły (1), on (1), czwartek (1)</t>
         </is>
       </c>
     </row>
@@ -1946,97 +1946,97 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>mój (5), mieć (3), ten (1), czekać (1), gdzie (1), ty (1), rano (1)</t>
+          <t>mój (4), mieć (3), ten (2), czekać (1), gdzie (1), ty (1), rano (1)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ROZUMIEĆ</t>
+          <t>KOCHAĆ</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>11</v>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>nie (8), ty (2), zawsze (1)</t>
+          <t>bardzo (2), on (1), my (1), wy (1), zawsze (1)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KOCHAĆ</t>
+          <t>ZDROWY</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>11</v>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>bardzo (2), on (1), my (1), wy (1), zawsze (1)</t>
+          <t>bardzo (3), dzisiaj (2), wesoły (2), on (1), stary (1), jeść (1), nie (1)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ZDROWY</t>
+          <t>WTOREK</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>11</v>
       </c>
       <c r="C88" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>bardzo (3), dzisiaj (2), wesoły (2), on (1), stary (1), jeść (1), nie (1)</t>
+          <t>noc (1), kobieta (1), dlaczego (1), dzisiaj (1), szkoła (1), ty (1), mówić (1), ten (1), zdrowy (1)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>WTOREK</t>
+          <t>JUŻ</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C89" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>noc (1), kobieta (1), dlaczego (1), dzisiaj (1), szkoła (1), ty (1), mówić (1), ten (1), zdrowy (1)</t>
+          <t>wy (2), chcieć (1), babcia (1), rano (1), iść (1), kiedy (1), telefon (1), dziadek (1)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>JUŻ</t>
+          <t>ROZUMIEĆ</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>10</v>
       </c>
       <c r="C90" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>wy (2), chcieć (1), babcia (1), rano (1), iść (1), kiedy (1), telefon (1), dziadek (1)</t>
+          <t>nie (7), ty (2), zawsze (1)</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Brak (zawsze na początku zdania)</t>
+          <t>None (always at the start of a sentence)</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Brak (zawsze na początku zdania)</t>
+          <t>None (always at the start of a sentence)</t>
         </is>
       </c>
     </row>
@@ -2140,11 +2140,11 @@
         <v>9</v>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ten (3), cały (2), nowy (1), dzisiaj (1), który (1), już (1)</t>
+          <t>ten (3), już (3), nowy (1), dzisiaj (1), który (1)</t>
         </is>
       </c>
     </row>
@@ -2241,18 +2241,36 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CAŁY</t>
+          <t>NASZ</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>None (always at the start of a sentence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>WASZ</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
         <v>1</v>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>już (2)</t>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>None (always at the start of a sentence)</t>
         </is>
       </c>
     </row>

--- a/Sentences/report.xlsx
+++ b/Sentences/report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,50 +445,50 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gdzie (8), rano (5), widzieć (3), migać (3), czekać (3), samochód (3), kochać (3), dzień (2), telefon (2), myśleć (2), kot (2), szkoła (2), noc (2), spać (1), mieć (1), pomysł (1), wczoraj (1), kiedy (1), tata (1), klucz (1), mówić (1), ja (1), lubić (1), dzisiaj (1), pomóc (1), zimny (1), mama (1), pies (1), brat (1), czas (1), pamiętać (1), woda (1), słyszeć (1), pić (1), kawa (1), iść (1), pracować (1), książka (1), ty (1), co (1)</t>
+          <t>gdzie (8), rano (5), widzieć (3), migać (3), czekać (3), samochód (3), kochać (3), mieć (2), dzień (2), telefon (2), myśleć (2), kot (2), szkoła (2), pamiętać (2), spać (1), pomysł (1), wczoraj (1), kiedy (1), tata (1), klucz (1), mówić (1), ja (1), lubić (1), dzisiaj (1), przepraszać (1), pomóc (1), zimny (1), mama (1), pies (1), brat (1), kupić (1), czas (1), noc (1), woda (1), słyszeć (1), pić (1), kawa (1), iść (1), książka (1), ty (1), co (1)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dlaczego (6), co (5), dziękować (4), kupić (4), czekać (4), ja (4), móc (3), kiedy (3), rano (2), iść (2), gdzie (2), książka (2), dzisiaj (1), jak (1), wiedzieć (1), mówić (1), smutny (1), myśleć (1), woda (1), dom (1), widzieć (1), kto (1), przepraszać (1), przyjaciel (1), jutro (1), wieczór (1), herbata (1), kawa (1), kobieta (1), pić (1), pies (1), wczoraj (1), chcieć (1), kot (1)</t>
+          <t>kupić (18), dlaczego (6), kochać (5), mieć (4), ty (4), chcieć (3), myśleć (3), mówić (2), słyszeć (2), pomysł (2), jak (2), migać (1), twój (1), stary (1), dziękować (1), dzisiaj (1), herbata (1), pieniądz (1), tata (1), gdzie (1), zimny (1), klucz (1), spać (1), czekać (1), nie (1), robić (1), ja (1), widzieć (1), co (1), środa (1), lubić (1)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>kupić (20), dlaczego (6), kochać (4), ty (4), chcieć (3), myśleć (3), mieć (3), mówić (2), słyszeć (2), jak (2), migać (1), twój (1), stary (1), dziękować (1), dzisiaj (1), pieniądz (1), tata (1), gdzie (1), zimny (1), klucz (1), spać (1), czekać (1), nie (1), robić (1), ja (1), widzieć (1), co (1), środa (1), lubić (1)</t>
+          <t>dlaczego (6), co (5), dziękować (4), kupić (4), czekać (4), ja (4), kiedy (3), rano (2), móc (2), iść (2), kobieta (2), dzisiaj (1), jak (1), wiedzieć (1), mówić (1), smutny (1), myśleć (1), woda (1), dom (1), widzieć (1), kto (1), przepraszać (1), przyjaciel (1), jutro (1), wieczór (1), herbata (1), kawa (1), książka (1), pić (1), pies (1), wczoraj (1), chcieć (1), kot (1), gdzie (1)</t>
         </is>
       </c>
     </row>
@@ -499,14 +499,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C5" t="n">
         <v>34</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>dziadek (7), ja (6), wczoraj (5), dzisiaj (5), ty (5), przepraszać (4), on (3), mężczyzna (2), wy (2), kot (2), rano (2), chory (2), my (2), dlaczego (2), kolega (1), brat (1), zmęczony (1), pracować (1), kiedy (1), widzieć (1), pies (1), siostra (1), często (1), pieniądz (1), jutro (1), noc (1), rok (1), zdrowy (1), książka (1), mówić (1), samochód (1), tata (1), pić (1), spać (1)</t>
+          <t>ja (6), dziadek (6), wczoraj (5), ty (5), dzisiaj (4), przepraszać (4), on (3), mężczyzna (2), wy (2), kot (2), rano (2), chory (2), my (2), dlaczego (2), kolega (1), brat (1), zmęczony (1), pracować (1), kiedy (1), widzieć (1), pies (1), siostra (1), często (1), pieniądz (1), jutro (1), noc (1), rok (1), zdrowy (1), książka (1), mówić (1), samochód (1), tata (1), pić (1), spać (1)</t>
         </is>
       </c>
     </row>
@@ -517,14 +517,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C6" t="n">
         <v>44</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>dzisiaj (7), ja (6), wczoraj (3), jak (3), my (3), który (2), pies (2), on (2), siostra (2), jutro (2), dziadek (2), praca (2), tata (2), rano (2), przyjaciel (2), słyszeć (1), wy (1), chory (1), jeść (1), ty (1), dom (1), wieczór (1), herbata (1), lubić (1), często (1), wiedzieć (1), kolega (1), czas (1), mężczyzna (1), kobieta (1), pracować (1), kiedy (1), mieć (1), już (1), rok (1), brat (1), noc (1), dlaczego (1), kot (1), myśleć (1), zawsze (1), ten (1), poniedziałek (1), środa (1)</t>
+          <t>dzisiaj (7), ja (5), wczoraj (3), jak (3), my (3), który (2), on (2), jutro (2), dziadek (2), praca (2), tata (2), już (2), rano (2), przyjaciel (2), słyszeć (1), wy (1), pies (1), chory (1), jeść (1), ty (1), dom (1), wieczór (1), herbata (1), siostra (1), lubić (1), często (1), wiedzieć (1), kolega (1), czas (1), mężczyzna (1), kobieta (1), pracować (1), kiedy (1), mieć (1), rok (1), brat (1), noc (1), dlaczego (1), kot (1), myśleć (1), zawsze (1), ten (1), poniedziałek (1), środa (1)</t>
         </is>
       </c>
     </row>
@@ -535,14 +535,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>pić (6), pomóc (4), przepraszać (3), czekać (3), kupić (3), mieć (3), dom (3), ty (3), chcieć (2), co (2), nie (2), dobry (2), iść (2), uczyć (2), spać (2), migać (1), myśleć (1), móc (1), kiedy (1), poniedziałek (1), robić (1), noc (1), czas (1), dlaczego (1), rozumieć (1), rok (1), ważny (1), wczoraj (1), rano (1), środa (1)</t>
+          <t>pić (6), pomóc (4), przepraszać (3), czekać (3), kupić (3), mieć (3), dom (3), chcieć (2), co (2), nie (2), dobry (2), uczyć (2), ty (2), spać (2), migać (1), myśleć (1), móc (1), iść (1), kiedy (1), poniedziałek (1), robić (1), noc (1), czas (1), dlaczego (1), rozumieć (1), ważny (1), wczoraj (1), środa (1)</t>
         </is>
       </c>
     </row>
@@ -553,14 +553,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>wczoraj (7), dzisiaj (6), jutro (6), poniedziałek (4), zawsze (4), wtorek (3), spać (2), kawa (2), mówić (2), iść (2), woda (2), widzieć (2), mieć (2), czekać (2), ty (2), robić (1), brat (1), pić (1), pracować (1), pamiętać (1), jeść (1), kiedy (1), chcieć (1), ja (1), klucz (1), pies (1), chory (1), herbata (1), samochód (1), urodziny (1), czas (1), kochać (1), szkoła (1), czwartek (1), środa (1)</t>
+          <t>wczoraj (7), dzisiaj (6), jutro (6), poniedziałek (4), zawsze (4), wtorek (3), spać (2), kawa (2), mówić (2), iść (2), woda (2), widzieć (2), mieć (2), czekać (2), ty (2), robić (1), brat (1), pić (1), pracować (1), pamiętać (1), jeść (1), kiedy (1), chcieć (1), ja (1), klucz (1), pies (1), chory (1), samochód (1), urodziny (1), czas (1), kochać (1), szkoła (1), czwartek (1), środa (1)</t>
         </is>
       </c>
     </row>
@@ -571,14 +571,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>nie (16), brat (6), chcieć (4), przyjaciel (4), ty (3), zawsze (3), kto (3), pracować (3), kiedy (2), wczoraj (2), dziadek (1), babcia (1), mężczyzna (1), lubić (1), kobieta (1), wesoły (1), siostra (1), widzieć (1), tata (1), dziękować (1), móc (1), często (1), czas (1), praca (1), pamiętać (1), pić (1), pies (1), musieć (1)</t>
+          <t>nie (16), brat (6), chcieć (4), przyjaciel (4), zawsze (3), kto (3), pracować (3), ty (2), kiedy (2), który (2), wczoraj (2), dziadek (1), babcia (1), mężczyzna (1), lubić (1), kobieta (1), wesoły (1), siostra (1), widzieć (1), tata (1), dziękować (1), móc (1), często (1), czas (1), praca (1), pamiętać (1), pić (1), pies (1), musieć (1)</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" t="n">
         <v>20</v>
@@ -625,14 +625,14 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>mieć (10), ten (8), musieć (5), lubić (4), dom (3), bardzo (3), wczoraj (3), jak (2), dzisiaj (2), rano (2), zawsze (2), samochód (2), chcieć (2), kochać (1), często (1), ty (1), jeść (1), pić (1), uczyć (1), kupić (1), iść (1), wieczór (1), kot (1), pamiętać (1)</t>
+          <t>mieć (10), ten (7), musieć (5), lubić (4), dom (3), bardzo (3), wczoraj (3), jak (2), dzisiaj (2), rano (2), zawsze (2), chcieć (2), kochać (1), często (1), ty (1), samochód (1), jeść (1), pić (1), teraz (1), uczyć (1), kupić (1), iść (1), wieczór (1), kot (1), pamiętać (1)</t>
         </is>
       </c>
     </row>
@@ -643,14 +643,14 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>nowy (12), stary (10), duży (4), czekać (4), rano (3), iść (2), mieć (2), klucz (2), pies (2), ja (2), brat (2), my (1), nie (1), wieczór (1), dziadek (1), już (1), woda (1), pracować (1), wczoraj (1), praca (1), on (1), tata (1), uczyć (1), mój (1), środa (1)</t>
+          <t>nowy (11), stary (10), duży (4), czekać (4), rano (3), iść (2), mieć (2), klucz (2), pies (2), ja (2), brat (2), my (1), nie (1), wieczór (1), dziadek (1), już (1), woda (1), pracować (1), praca (1), on (1), tata (1), uczyć (1), środa (1)</t>
         </is>
       </c>
     </row>
@@ -679,32 +679,32 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C15" t="n">
         <v>18</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ten (9), twój (7), mój (6), mieć (5), pieniądz (4), kupić (4), pomysł (2), ja (2), dom (1), czekać (1), migać (1), pracować (1), rano (1), dzisiaj (1), bardzo (1), jutro (1), spać (1), iść (1)</t>
+          <t>ten (8), mój (6), mieć (5), twój (5), pieniądz (4), kupić (4), pomysł (2), ja (2), dom (1), czekać (1), migać (1), pracować (1), rano (1), dzisiaj (1), bardzo (1), jutro (1), taki (1), iść (1)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TWÓJ</t>
+          <t>STARY</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>dlaczego (3), myśleć (3), gdzie (2), pamiętać (2), wczoraj (2), migać (2), pić (2), duży (1), ty (1), telefon (1), kobieta (1), mężczyzna (1), kiedy (1), mówić (1), dziękować (1), mały (1), uczyć (1), dom (1), pracować (1), kawa (1), jak (1), rano (1), klucz (1), czwartek (1), wieczór (1)</t>
+          <t>ten (15), mój (10), duży (2), ja (2), książka (2), mieć (1), telefon (1), już (1), taki (1), spać (1), jutro (1), babcia (1), kolega (1), iść (1), kupić (1), pies (1), brat (1), twój (1)</t>
         </is>
       </c>
     </row>
@@ -715,14 +715,14 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C17" t="n">
         <v>22</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>zawsze (6), często (4), rano (4), dzisiaj (3), chcieć (3), duży (3), lubić (3), poniedziałek (2), wczoraj (2), kiedy (2), dziadek (2), pamiętać (2), ja (1), mężczyzna (1), on (1), noc (1), jeść (1), kochać (1), woda (1), czas (1), kolega (1), musieć (1)</t>
+          <t>zawsze (4), często (4), duży (4), dzisiaj (3), chcieć (3), lubić (3), rano (3), poniedziałek (2), wczoraj (2), kiedy (2), dziadek (2), pamiętać (2), ja (1), mężczyzna (1), on (1), noc (1), jeść (1), kochać (1), wtorek (1), czas (1), kolega (1), musieć (1)</t>
         </is>
       </c>
     </row>
@@ -733,248 +733,248 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" t="n">
         <v>19</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>chcieć (7), rano (5), wczoraj (4), kolega (3), tata (3), kiedy (3), móc (2), dziadek (2), myśleć (2), jak (2), brat (2), już (1), pieniądz (1), mama (1), ty (1), szkoła (1), mężczyzna (1), wieczór (1), on (1)</t>
+          <t>chcieć (7), rano (5), wczoraj (4), kolega (3), tata (3), kiedy (3), móc (2), dziadek (2), myśleć (2), jak (2), już (1), pieniądz (1), mama (1), ty (1), szkoła (1), mężczyzna (1), wieczór (1), brat (1), który (1)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STARY</t>
+          <t>IŚĆ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ten (15), mój (10), duży (2), ja (2), książka (2), mieć (1), telefon (1), już (1), taki (1), spać (1), jutro (1), babcia (1), kolega (1), iść (1), kupić (1), pies (1), brat (1), twój (1)</t>
+          <t>dzisiaj (4), rano (4), ty (4), musieć (3), teraz (3), pies (3), ja (2), chcieć (2), móc (2), kiedy (2), pomysł (2), już (1), kobieta (1), brat (1), poniedziałek (1), my (1), zmęczony (1), jutro (1), wieczór (1), chory (1), samochód (1), zdrowy (1), mężczyzna (1), czwartek (1)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IŚĆ</t>
+          <t>TWÓJ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C20" t="n">
         <v>25</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>dzisiaj (4), rano (4), ty (4), pies (3), ja (2), musieć (2), teraz (2), chcieć (2), móc (2), kiedy (2), pomysł (2), już (1), kobieta (1), brat (1), poniedziałek (1), my (1), zmęczony (1), jutro (1), wieczór (1), chory (1), samochód (1), on (1), zdrowy (1), mężczyzna (1), czwartek (1)</t>
+          <t>dlaczego (3), gdzie (2), pamiętać (2), myśleć (2), wczoraj (2), duży (1), ty (1), telefon (1), kobieta (1), mężczyzna (1), kiedy (1), mówić (1), dziękować (1), mały (1), pić (1), uczyć (1), dom (1), pracować (1), kawa (1), jak (1), rano (1), migać (1), klucz (1), czwartek (1), wieczór (1)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PIES</t>
+          <t>ZAWSZE</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>mały (11), mój (6), duży (4), twój (3), ten (3), nowy (2), stary (2), wesoły (2), zmęczony (1), mama (1), słyszeć (1), mężczyzna (1), ty (1), dom (1), praca (1), rano (1), brat (1)</t>
+          <t>ty (6), pies (2), brat (2), przyjaciel (2), babcia (2), rano (1), mężczyzna (1), on (1), szkoła (1), dom (1), dziadek (1), pamiętać (1), rok (1), kot (1), dlaczego (1), wtorek (1)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ZAWSZE</t>
+          <t>DLACZEGO</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ty (6), pies (2), brat (2), przyjaciel (2), babcia (2), rano (1), mężczyzna (1), on (1), szkoła (1), dom (1), dziadek (1), pamiętać (1), rok (1), kot (1), ja (1), my (1), dlaczego (1), wtorek (1)</t>
+          <t>wiedzieć (5), rozumieć (1), uczyć (1), pamiętać (1)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DLACZEGO</t>
+          <t>PRACA</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>39</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>wiedzieć (5), rozumieć (1), uczyć (1), pamiętać (1)</t>
+          <t>iść (10), mój (4), kolega (3), rano (3), ja (2), nowy (2), dobry (2), robić (1), telefon (1), dzień (1), smutny (1), czas (1), pomysł (1), woda (1), zmęczony (1), kawa (1), stary (1), ty (1)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BRAT</t>
+          <t>PIES</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>39</v>
       </c>
       <c r="C24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>mój (15), chory (3), mały (3), twój (2), zmęczony (1), siostra (1), dom (1), nasz (1), gdzie (1), on (1), nowy (1), spać (1), ty (1), urodziny (1)</t>
+          <t>mały (10), mój (6), duży (4), twój (3), ten (3), stary (2), wesoły (2), zmęczony (1), mama (1), słyszeć (1), mężczyzna (1), ty (1), praca (1), nowy (1), rano (1), brat (1)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRACA</t>
+          <t>BRAT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C25" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>iść (9), mój (4), kolega (3), rano (3), ja (2), nowy (2), dobry (2), robić (1), telefon (1), dzień (1), smutny (1), czas (1), pomóc (1), pomysł (1), woda (1), zmęczony (1), kawa (1), stary (1), ty (1)</t>
+          <t>mój (15), mały (3), chory (2), twój (2), on (2), zmęczony (1), siostra (1), dom (1), gdzie (1), spać (1), ty (1), urodziny (1)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SZKOŁA</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>iść (6), nowy (5), ja (3), nie (2), migać (2), stary (2), wczoraj (1), dzisiaj (1), uczyć (1), klucz (1), zmęczony (1), ty (1), kobieta (1), kot (1), poniedziałek (1), pracować (1), rano (1), dzień (1), robić (1), kawa (1), woda (1), pies (1)</t>
+          <t>dlaczego (5), kiedy (3), co (2), jak (2), myśleć (2), widzieć (1), nie (1), dziękować (1), mama (1), czas (1), babcia (1), szkoła (1), dom (1), kto (1), wy (1)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DOBRY</t>
+          <t>SZKOŁA</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>35</v>
       </c>
       <c r="C27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>bardzo (15), jak (2), ty (2), dzień (1), mieć (1), wczoraj (1), myśleć (1), kupić (1), mój (1), zawsze (1), ten (1), chcieć (1), nie (1), dziękować (1), ważny (1), my (1), taki (1), tata (1), pić (1)</t>
+          <t>iść (6), nowy (5), ja (3), nie (2), stary (2), wczoraj (1), migać (1), dzisiaj (1), uczyć (1), klucz (1), zmęczony (1), ty (1), kobieta (1), kot (1), poniedziałek (1), pracować (1), rano (1), dzień (1), robić (1), pies (1)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>DOBRY</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>33</v>
       </c>
       <c r="C28" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>kiedy (5), dlaczego (5), co (2), jak (2), myśleć (2), widzieć (1), nie (1), dziękować (1), czas (1), babcia (1), szkoła (1), dom (1)</t>
+          <t>bardzo (15), jak (2), ty (2), dzień (1), mieć (1), wczoraj (1), myśleć (1), kupić (1), mój (1), zawsze (1), ten (1), chcieć (1), nie (1), dziękować (1), my (1), taki (1), tata (1)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DZIADEK</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>31</v>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>dom (6), babcia (5), mój (5), stary (1), wczoraj (1), kiedy (1), dlaczego (1), kawa (1), rano (1), wieczór (1)</t>
+          <t>gdzie (3), co (2), dzień (2), kiedy (1), chcieć (1), ważny (1), dlaczego (1), iść (1), czas (1), rok (1), który (1), wtorek (1)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SAMOCHÓD</t>
+          <t>DZIADEK</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>stary (13), nowy (4), mały (3), ten (3), twój (2), telefon (1), ja (1), tata (1), taki (1), mężczyzna (1), duży (1)</t>
+          <t>dom (6), babcia (5), mój (4), stary (1), wczoraj (1), kiedy (1), dlaczego (1), kawa (1), rano (1), wieczór (1)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>SAMOCHÓD</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>gdzie (3), co (2), dzień (2), kiedy (1), chcieć (1), ważny (1), dlaczego (1), iść (1), czas (1), rok (1), myśleć (1), wtorek (1)</t>
+          <t>stary (13), nowy (4), ten (3), mały (2), twój (2), telefon (1), ja (1), tata (1), taki (1), mężczyzna (1), duży (1)</t>
         </is>
       </c>
     </row>
@@ -985,14 +985,14 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C32" t="n">
         <v>9</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>pić (7), gorący (7), ja (4), zimny (3), czas (3), iść (2), ile (2), herbata (1), duży (1)</t>
+          <t>pić (7), gorący (7), zimny (3), ja (3), czas (3), iść (2), ile (2), herbata (1), duży (1)</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C33" t="n">
         <v>11</v>
@@ -1017,90 +1017,90 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MAŁY</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ten (8), mój (5), mieć (2), kupić (2), bardzo (1), ty (1), woda (1), telefon (1), twój (1), kobieta (1), wasz (1), on (1), wieczór (1), iść (1), mężczyzna (1)</t>
+          <t>wczoraj (7), kawa (2), pracować (2), praca (2), co (1), kolega (1), zimny (1), herbata (1), nie (1), woda (1), spać (1), dziadek (1), jutro (1), środa (1)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>GDZIE</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C35" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>wczoraj (7), kawa (2), pracować (2), praca (2), co (1), kolega (1), zimny (1), herbata (1), nie (1), woda (1), spać (1), dziadek (1), jutro (1), środa (1)</t>
+          <t>wiedzieć (6), dzisiaj (1), przepraszać (1)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GDZIE</t>
+          <t>LUBIĆ</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>wiedzieć (6), dzisiaj (1)</t>
+          <t>bardzo (9), brat (3), nie (3), ty (2), my (2), on (1), ja (1), pies (1), rano (1), kobieta (1), babcia (1), kot (1)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LUBIĆ</t>
+          <t>CZEKAĆ</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>bardzo (9), nie (4), brat (3), ty (2), my (2), on (1), ja (1), pies (1), rano (1), kobieta (1), babcia (1), kot (1)</t>
+          <t>mężczyzna (3), musieć (2), ty (2), przyjaciel (2), dom (1), brat (1), siostra (1), pies (1), rano (1), kolega (1), zawsze (1), wczoraj (1), kobieta (1), on (1), szkoła (1), babcia (1)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SPAĆ</t>
+          <t>MAŁY</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>26</v>
       </c>
       <c r="C38" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>iść (5), duży (4), lubić (4), kot (3), często (3), dzisiaj (2), chcieć (1), już (1), gdzie (1), nie (1), noc (1)</t>
+          <t>ten (7), mój (4), mieć (2), kupić (2), on (2), bardzo (1), ty (1), woda (1), telefon (1), twój (1), kobieta (1), wieczór (1), iść (1)</t>
         </is>
       </c>
     </row>
@@ -1111,122 +1111,122 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C39" t="n">
         <v>14</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>mały (6), stary (3), pies (3), ten (2), duży (2), nowy (1), mieć (1), smutny (1), dom (1), noc (1), on (1), lubić (1), mówić (1), kiedy (1)</t>
+          <t>mały (6), stary (3), pies (3), ten (2), nowy (1), mieć (1), smutny (1), dom (1), noc (1), duży (1), on (1), lubić (1), mówić (1), kiedy (1)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CZEKAĆ</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C40" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>mężczyzna (3), musieć (2), ty (2), przyjaciel (2), dom (1), brat (1), siostra (1), pies (1), rano (1), kolega (1), zawsze (1), wczoraj (1), kobieta (1), on (1), szkoła (1), babcia (1)</t>
+          <t>rozumieć (6), słyszeć (6), pamiętać (4), myśleć (3), wiedzieć (2)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>WIEDZIEĆ</t>
+          <t>PIENIĄDZ</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>25</v>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ty (3), ja (3), chcieć (3), zawsze (2), dobry (2), wy (1), kto (1), nie (1), musieć (1), już (1)</t>
+          <t>duży (9), mieć (6), ile (4), mój (3), czas (1), teraz (1), samochód (1)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>UCZYĆ</t>
+          <t>SPAĆ</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C42" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>lubić (3), musieć (2), chcieć (2), siostra (1), szkoła (1), wy (1), dobry (1), praca (1), on (1), zawsze (1), rano (1), ty (1), pamiętać (1), wczoraj (1), jak (1), środa (1)</t>
+          <t>iść (5), duży (4), lubić (3), kot (3), dzisiaj (2), często (2), chcieć (1), już (1), gdzie (1), nie (1), noc (1)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>WIEDZIEĆ</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>rozumieć (6), słyszeć (6), pamiętać (4), myśleć (3), wiedzieć (2)</t>
+          <t>ty (3), ja (3), chcieć (3), zawsze (2), dobry (2), wy (1), kto (1), nie (1), musieć (1), już (1)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>WESOŁY</t>
+          <t>UCZYĆ</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>bardzo (4), zdrowy (2), dzisiaj (2), twój (2), ten (2), dzień (1), taki (1), dobry (1), zawsze (1), myśleć (1), urodziny (1), kto (1), herbata (1), kolega (1)</t>
+          <t>lubić (3), musieć (2), chcieć (2), siostra (1), szkoła (1), wy (1), dobry (1), praca (1), on (1), zawsze (1), rano (1), ty (1), pamiętać (1), wczoraj (1), środa (1), teraz (1)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PIENIĄDZ</t>
+          <t>WESOŁY</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>duży (9), mieć (7), ile (4), mój (3), czas (1), samochód (1)</t>
+          <t>bardzo (4), zdrowy (2), dzisiaj (2), ten (2), dzień (1), taki (1), dobry (1), zawsze (1), myśleć (1), urodziny (1), twój (1), kto (1), herbata (1), kolega (1)</t>
         </is>
       </c>
     </row>
@@ -1237,50 +1237,50 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C46" t="n">
         <v>9</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>nowy (9), stary (4), który (2), twój (2), mój (2), kupić (2), ważny (1), dzisiaj (1), mały (1)</t>
+          <t>nowy (8), stary (4), który (2), twój (2), mój (2), kupić (2), ważny (1), dzisiaj (1), ten (1)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MIGAĆ</t>
+          <t>TATA</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>uczyć (16), chcieć (2), myśleć (1), teraz (1), dobry (1), ja (1), on (1), mężczyzna (1)</t>
+          <t>mój (6), czekać (3), twój (2), samochód (2), ty (1), już (1), on (1), książka (1), dziękować (1), wesoły (1), stary (1)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>WODA</t>
+          <t>MÓWIĆ</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>gorący (5), pić (4), zimny (4), gdzie (2), dziękować (1), jeść (1), dlaczego (1), duży (1), ile (1), dziadek (1), ja (1), dobry (1)</t>
+          <t>co (5), ja (4), ty (2), tata (2), babcia (2), my (1), noc (1), duży (1), czas (1), wczoraj (1), on (1), rano (1), lubić (1)</t>
         </is>
       </c>
     </row>
@@ -1291,248 +1291,248 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C49" t="n">
         <v>13</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>urodziny (3), dzisiaj (2), zawsze (2), pieniądz (2), pracować (2), dlaczego (1), migać (1), samochód (1), dom (1), dziadek (1), jeść (1), brat (1), wczoraj (1)</t>
+          <t>urodziny (3), dzisiaj (2), zawsze (2), pieniądz (2), dlaczego (1), pracować (1), migać (1), samochód (1), dom (1), dziadek (1), jeść (1), brat (1), wczoraj (1)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MYŚLEĆ</t>
+          <t>JUTRO</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>zawsze (4), noc (4), ty (2), często (2), duży (2), słyszeć (1), mama (1), dzisiaj (1), dlaczego (1)</t>
+          <t>robić (2), jeść (1), mieć (1), dzisiaj (1), pomysł (1), chory (1), rozumieć (1)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TATA</t>
+          <t>CZAS</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>23</v>
       </c>
       <c r="C51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>mój (6), czekać (3), twój (2), samochód (2), ty (1), klucz (1), on (1), książka (1), dziękować (1), wesoły (1), stary (1)</t>
+          <t>mieć (7), duży (3), ja (3), ten (3), ile (2), teraz (1), ważny (1), dlaczego (1), rok (1), dzisiaj (1)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PRZYJACIEL</t>
+          <t>KSIĄŻKA</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>23</v>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>mój (10), twój (5), dobry (3), wesoły (1), stary (1), mały (1), nowy (1), książka (1)</t>
+          <t>ten (7), nowy (4), duży (3), mały (2), mój (1), dobry (1), ja (1), ile (1), ty (1), jeść (1), pieniądz (1)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MÓWIĆ</t>
+          <t>PRZYJACIEL</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C53" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>co (5), ja (4), ty (2), tata (2), babcia (2), my (1), noc (1), duży (1), czas (1), wczoraj (1), on (1), rano (1), lubić (1)</t>
+          <t>mój (10), twój (5), dobry (3), stary (1), mały (1), nowy (1), książka (1)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PRACOWAĆ</t>
+          <t>MIGAĆ</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C54" t="n">
         <v>8</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>duży (10), rano (3), chcieć (2), musieć (2), móc (2), ty (2), iść (1), lubić (1)</t>
+          <t>uczyć (14), chcieć (2), myśleć (1), teraz (1), dobry (1), ja (1), on (1), mężczyzna (1)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>JUTRO</t>
+          <t>WODA</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>robić (2), jeść (1), mieć (1), dzisiaj (1), pomysł (1), chory (1), wiedzieć (1)</t>
+          <t>gorący (5), pić (4), zimny (4), gdzie (2), dziękować (1), jeść (1), dlaczego (1), duży (1), dziadek (1), ja (1)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CZAS</t>
+          <t>KOLEGA</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>mieć (7), duży (3), ja (3), ten (3), ile (2), teraz (1), ważny (1), dlaczego (1), rok (1), dzisiaj (1)</t>
+          <t>mój (6), twój (5), wesoły (1), noc (1), dobry (1), chcieć (1), stary (1), wieczór (1), kawa (1)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KSIĄŻKA</t>
+          <t>MYŚLEĆ</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C57" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ten (7), nowy (4), duży (3), mały (2), mój (1), dobry (1), ja (1), ile (1), ty (1), jeść (1), pieniądz (1)</t>
+          <t>zawsze (4), noc (4), ty (2), często (2), duży (2), słyszeć (1), mama (1), dzisiaj (1), dlaczego (1)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MĘŻCZYZNA</t>
+          <t>GORĄCY</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>22</v>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ten (6), wesoły (3), smutny (2), stary (2), herbata (1), kobieta (1)</t>
+          <t>pić (6), ten (3), lubić (2), dobry (2), dzisiaj (1), ja (1), duży (1), taki (1), kupić (1), robić (1), czekać (1), woda (1), dom (1)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KOLEGA</t>
+          <t>SMUTNY</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>mój (6), twój (5), wesoły (1), noc (1), dobry (1), chcieć (1), stary (1), wieczór (1), kawa (1)</t>
+          <t>bardzo (6), taki (2), wczoraj (1), mały (1), dlaczego (1), ja (1), zimny (1), dzisiaj (1), nie (1), on (1), zmęczony (1), zawsze (1)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GORĄCY</t>
+          <t>MĘŻCZYZNA</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C60" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>pić (6), ten (3), lubić (2), dobry (2), dzisiaj (1), ja (1), duży (1), herbata (1), kupić (1), robić (1), czekać (1), woda (1), dom (1)</t>
+          <t>ten (6), wesoły (3), smutny (2), stary (2), herbata (1), kobieta (1)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SMUTNY</t>
+          <t>PRACOWAĆ</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>21</v>
       </c>
       <c r="C61" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>bardzo (6), taki (2), wczoraj (1), mały (1), dlaczego (1), ja (1), zimny (1), dzisiaj (1), nie (1), on (1), zmęczony (1), zawsze (1)</t>
+          <t>duży (9), rano (3), chcieć (2), musieć (2), móc (2), iść (1), ty (1), lubić (1)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HERBATA</t>
+          <t>MUSIEĆ</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>21</v>
       </c>
       <c r="C62" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>gorący (7), pić (4), ja (2), kawa (1), zimny (1), ten (1), kupić (1), iść (1), my (1), dobry (1), ty (1)</t>
+          <t>zawsze (2), ty (2), ja (1), pomóc (1), czas (1), my (1), szkoła (1), dzień (1), zmęczony (1), klucz (1), mama (1), brat (1), kto (1), pieniądz (1), rano (1), praca (1)</t>
         </is>
       </c>
     </row>
@@ -1557,576 +1557,576 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DZIEŃ</t>
+          <t>ZMĘCZONY</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>20</v>
       </c>
       <c r="C64" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>dobry (4), gorący (3), nowy (2), ważny (2), wesoły (2), zimny (1), pracować (1), spać (1), smutny (1), ten (1), dom (1)</t>
+          <t>bardzo (8), dzisiaj (2), ty (1), ja (1), taki (1), noc (1), często (1), nie (1), wieczór (1)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ZMĘCZONY</t>
+          <t>SIOSTRA</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>bardzo (8), dzisiaj (2), ty (1), taki (1), noc (1), nie (1), wieczór (1)</t>
+          <t>mój (6), twój (5), mama (1), smutny (1), wesoły (1), książka (1), on (1), czwartek (1)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MUSIEĆ</t>
+          <t>DZIEŃ</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C66" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ja (2), zawsze (2), ty (2), pomóc (1), czas (1), my (1), szkoła (1), klucz (1), brat (1), kto (1), pieniądz (1), rano (1)</t>
+          <t>dobry (4), gorący (3), nowy (2), ważny (2), wesoły (2), zimny (1), pracować (1), spać (1), smutny (1), ten (1), dom (1)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SIOSTRA</t>
+          <t>HERBATA</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>mój (5), twój (5), mama (1), smutny (1), wesoły (1), on (1), czwartek (1)</t>
+          <t>gorący (7), ja (2), pić (2), kawa (1), zimny (1), ten (1), kupić (1), teraz (1), iść (1), my (1), dobry (1), ty (1)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>WIECZÓR</t>
+          <t>CHORY</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>wczoraj (8), poniedziałek (4), jutro (2), ty (1), środa (1), czwartek (1)</t>
+          <t>bardzo (5), który (2), kiedy (1), zmęczony (1), ja (1), książka (1), jutro (1), kto (1), praca (1), nie (1), pies (1), pomóc (1)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CZĘSTO</t>
+          <t>KOBIETA</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>bardzo (6), mama (2), rano (1), zdrowy (1), brat (1), kobieta (1), pies (1)</t>
+          <t>ten (6), który (2), wesoły (1), mężczyzna (1), wieczór (1), chory (1)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PAMIĘTAĆ</t>
+          <t>CZĘSTO</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>nie (6), zawsze (2)</t>
+          <t>bardzo (5), mama (2), rano (1), zdrowy (1), brat (1), kobieta (1), środa (1), pies (1), siostra (1)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>KOBIETA</t>
+          <t>PAMIĘTAĆ</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ten (5), który (2), wesoły (1), mężczyzna (1), wieczór (1)</t>
+          <t>nie (6), zawsze (2), już (1)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>JEŚĆ</t>
+          <t>JUŻ</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C72" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>duży (4), dzisiaj (2), woda (1), czekać (1), myśleć (1), kobieta (1), iść (1), chcieć (1), pić (1), pamiętać (1), noc (1), pies (1)</t>
+          <t>wy (2), teraz (2), chcieć (1), babcia (1), rano (1), iść (1), klucz (1), siostra (1), kiedy (1), telefon (1), chory (1), kochać (1), on (1)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ZIMNY</t>
+          <t>MAMA</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>pić (7), bardzo (5), taki (2), ten (1), mężczyzna (1)</t>
+          <t>mój (2), twój (2), ty (1), środa (1), pomóc (1), gdzie (1), czas (1), samochód (1), dzień (1), chory (1), pracować (1), woda (1)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>JAK</t>
+          <t>JEŚĆ</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>wiedzieć (4), widzieć (3), rozumieć (1), słyszeć (1), pomysł (1)</t>
+          <t>duży (4), dzisiaj (2), woda (1), czekać (1), myśleć (1), kobieta (1), iść (1), chcieć (1), pić (1), pamiętać (1), noc (1), teraz (1), pies (1)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CHORY</t>
+          <t>ZIMNY</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>bardzo (5), kiedy (1), zmęczony (1), ja (1), dom (1), jutro (1), kto (1), praca (1), nie (1), pies (1)</t>
+          <t>pić (7), bardzo (5), taki (2), ten (2), mężczyzna (1)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MAMA</t>
+          <t>WIECZÓR</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C76" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>mój (2), twój (2), ty (1), środa (1), pomóc (1), gdzie (1), czas (1), samochód (1), książka (1), pracować (1), woda (1)</t>
+          <t>wczoraj (8), poniedziałek (4), jutro (2), ty (1), środa (1), czwartek (1)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DZIĘKOWAĆ</t>
+          <t>ROBIĆ</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>zawsze (2), bardzo (1), kobieta (1), ty (1), rano (1)</t>
+          <t>co (3), ile (3), chcieć (2), często (1), rok (1), środa (1), zdrowy (1), babcia (1), móc (1), dzisiaj (1), kochać (1)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>WIDZIEĆ</t>
+          <t>POMÓC</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>wieczór (3), wczoraj (2), dobry (1), my (1), nie (1), rano (1), ty (1)</t>
+          <t>wczoraj (3), ja (3), dzisiaj (2), my (1), kolega (1), bardzo (1), ty (1), móc (1), dziękować (1), on (1), jak (1)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SŁYSZEĆ</t>
+          <t>JAK</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C79" t="n">
         <v>4</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>nie (8), noc (2), często (2), ty (1)</t>
+          <t>wiedzieć (4), widzieć (3), rozumieć (2), słyszeć (1)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>POMÓC</t>
+          <t>ZDROWY</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>wczoraj (3), ja (3), dzisiaj (2), ty (2), my (1), kolega (1), bardzo (1), móc (1), dziękować (1)</t>
+          <t>bardzo (3), dzisiaj (2), taki (2), wesoły (2), on (1), stary (1), jeść (1), robić (1), ten (1), nie (1)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MÓC</t>
+          <t>POMYSŁ</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>nie (10), gdzie (1), pieniądz (1), duży (1)</t>
+          <t>nowy (4), dobry (3), mieć (3), zdrowy (3), twój (2), który (1)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>KTO</t>
+          <t>TAKI</t>
         </is>
       </c>
       <c r="B82" t="n">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
         <v>14</v>
       </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>wiedzieć (1)</t>
+          <t>kupić (3), noc (1), brat (1), rano (1), zawsze (1), ja (1), często (1), herbata (1), musieć (1), ty (1), przepraszać (1), rozumieć (1), już (1), czwartek (1)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>POMYSŁ</t>
+          <t>ŚRODA</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>mieć (4), dobry (3), nowy (3), twój (2), który (1)</t>
+          <t>gdzie (1), rano (1), ten (1), wy (1), praca (1), wtorek (1), pracować (1), wiedzieć (1), spać (1), zawsze (1)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>URODZINY</t>
+          <t>KTÓRY</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>pomysł (3), książka (2), twój (2), dzisiaj (2), mieć (2), jutro (1), mój (1)</t>
+          <t>kot (1), stary (1), pies (1), dziadek (1), książka (1), telefon (1), dom (1), klucz (1)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KLUCZ</t>
+          <t>ROZUMIEĆ</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C85" t="n">
         <v>7</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>mój (4), mieć (3), ten (2), czekać (1), gdzie (1), ty (1), rano (1)</t>
+          <t>nie (7), ty (2), wy (2), zawsze (1), teraz (1), już (1), uczyć (1)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>KOCHAĆ</t>
+          <t>DZIĘKOWAĆ</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C86" t="n">
         <v>5</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>bardzo (2), on (1), my (1), wy (1), zawsze (1)</t>
+          <t>zawsze (2), bardzo (1), kobieta (1), ty (1), rano (1)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ZDROWY</t>
+          <t>KTO</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C87" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>bardzo (3), dzisiaj (2), wesoły (2), on (1), stary (1), jeść (1), nie (1)</t>
+          <t>wiedzieć (1), chory (1)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>WTOREK</t>
+          <t>WIDZIEĆ</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C88" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>noc (1), kobieta (1), dlaczego (1), dzisiaj (1), szkoła (1), ty (1), mówić (1), ten (1), zdrowy (1)</t>
+          <t>wieczór (3), wczoraj (2), dobry (1), my (1), nie (1), rano (1), ty (1)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>JUŻ</t>
+          <t>ILE</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>wy (2), chcieć (1), babcia (1), rano (1), iść (1), kiedy (1), telefon (1), dziadek (1)</t>
+          <t>rok (1), przepraszać (1)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ROZUMIEĆ</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>nie (7), ty (2), zawsze (1)</t>
+          <t>dlaczego (3), kto (2), wiedzieć (1), kiedy (1), przepraszać (1), rok (1), mój (1)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ILE</t>
+          <t>SŁYSZEĆ</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>None (always at the start of a sentence)</t>
+          <t>nie (8), noc (2), często (2), ty (1)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>WAŻNY</t>
+          <t>KOCHAĆ</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>bardzo (5), ty (2), czekać (1), ten (1)</t>
+          <t>bardzo (2), już (2), on (1), my (1), wy (1), zawsze (1), teraz (1), herbata (1)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PRZEPRASZAĆ</t>
+          <t>WAŻNY</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>None (always at the start of a sentence)</t>
+          <t>bardzo (4), taki (3), czekać (1), mój (1), czwartek (1), rozumieć (1), ten (1), ty (1), my (1)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>KTÓRY</t>
+          <t>TERAZ</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>kot (1), stary (1)</t>
+          <t>mieć (2), musieć (2), wy (2), chcieć (1), móc (1), mężczyzna (1), my (1), pić (1), środa (1), migać (1), on (1)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>PRZEPRASZAĆ</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>dlaczego (3), kto (2), wiedzieć (1), kiedy (1)</t>
+          <t>None (always at the start of a sentence)</t>
         </is>
       </c>
     </row>
@@ -2137,140 +2137,104 @@
         </is>
       </c>
       <c r="B96" t="n">
+        <v>15</v>
+      </c>
+      <c r="C96" t="n">
         <v>9</v>
       </c>
-      <c r="C96" t="n">
-        <v>5</v>
-      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ten (3), już (3), nowy (1), dzisiaj (1), który (1)</t>
+          <t>już (3), ważny (3), ten (2), robić (2), nowy (1), dzisiaj (1), który (1), ile (1), rok (1)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TAKI</t>
+          <t>URODZINY</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C97" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>kupić (3), noc (1), brat (1), rano (1), zawsze (1), ja (1), musieć (1)</t>
+          <t>pomysł (3), książka (2), twój (2), dzisiaj (2), mieć (2), mój (2), jutro (1), on (1)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ŚRODA</t>
+          <t>KLUCZ</t>
         </is>
       </c>
       <c r="B98" t="n">
+        <v>15</v>
+      </c>
+      <c r="C98" t="n">
         <v>9</v>
       </c>
-      <c r="C98" t="n">
-        <v>5</v>
-      </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>gdzie (1), pracować (1), wiedzieć (1), spać (1), zawsze (1)</t>
+          <t>mój (3), mieć (3), ten (2), ważny (2), czekać (1), gdzie (1), ty (1), rano (1), iść (1)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CZWARTEK</t>
+          <t>MÓC</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C99" t="n">
         <v>5</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ten (1), urodziny (1), mieć (1), pomóc (1), jutro (1)</t>
+          <t>nie (9), gdzie (1), pieniądz (1), duży (1), ile (1)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ROBIĆ</t>
+          <t>WTOREK</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C100" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>co (3), chcieć (2), często (1), babcia (1), dzisiaj (1)</t>
+          <t>noc (1), kobieta (1), zimny (1), herbata (1), rano (1), dlaczego (1), dzisiaj (1), szkoła (1), ty (1), mówić (1), ten (1), zdrowy (1)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TERAZ</t>
+          <t>CZWARTEK</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>chcieć (1), mieć (1), móc (1), mężczyzna (1), my (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>NASZ</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>1</v>
-      </c>
-      <c r="C102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>None (always at the start of a sentence)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>WASZ</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>1</v>
-      </c>
-      <c r="C103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>None (always at the start of a sentence)</t>
+          <t>środa (3), ten (2), urodziny (2), robić (1), mieć (1), pomóc (1), jutro (1)</t>
         </is>
       </c>
     </row>
